--- a/table emigration per country by hand .xlsx
+++ b/table emigration per country by hand .xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/91d17e650f6003f9/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/91d17e650f6003f9/Documenti/BA3/Computational methods and tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_AD4DB114E441178AC67DF4DE4697C560683EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A84B49D8-8B72-4B87-BBE3-4B40F8C609C6}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="11_AD4DB114E441178AC67DF4DE4697C560683EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9574B480-4454-48B1-AC9C-2A4593EC766D}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
   <si>
     <t>united states</t>
   </si>
@@ -49,6 +49,21 @@
   </si>
   <si>
     <t>0,892</t>
+  </si>
+  <si>
+    <t>japan</t>
+  </si>
+  <si>
+    <t>0,725</t>
+  </si>
+  <si>
+    <t>0,667</t>
+  </si>
+  <si>
+    <t>0,676</t>
+  </si>
+  <si>
+    <t>0,709</t>
   </si>
 </sst>
 </file>
@@ -101,6 +116,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -366,7 +385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -429,6 +448,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1995</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>2000</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>2005</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>2010</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
